--- a/data/trans_orig/P1419-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2007</t>
+          <t>Población con diagnóstico de varices en las piernas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>39990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67583</t>
+          <t>69120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205934</t>
+          <t>200399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257587</t>
+          <t>257967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252439</t>
+          <t>251978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>317112</t>
+          <t>313166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>964140</t>
+          <t>962603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>992079</t>
+          <t>991733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1057526</t>
+          <t>1057146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1109179</t>
+          <t>1114714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2029723</t>
+          <t>2033669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2094396</t>
+          <t>2094857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24740</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49478</t>
+          <t>47756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87733</t>
+          <t>85555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128128</t>
+          <t>125146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115972</t>
+          <t>119380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165109</t>
+          <t>163981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1643935</t>
+          <t>1645657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1668673</t>
+          <t>1669784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1459545</t>
+          <t>1462527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1499940</t>
+          <t>1502118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3115977</t>
+          <t>3117105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3165114</t>
+          <t>3161706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>19950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40555</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55078</t>
+          <t>56361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530008</t>
+          <t>530423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545407</t>
+          <t>545318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435857</t>
+          <t>433823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456934</t>
+          <t>456462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>972742</t>
+          <t>971459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>998523</t>
+          <t>997711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>80228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118709</t>
+          <t>119234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>331117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>402469</t>
+          <t>402712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>422231</t>
+          <t>424119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>507266</t>
+          <t>505612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3157834</t>
+          <t>3157309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3194502</t>
+          <t>3196315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2976728</t>
+          <t>2976485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3049580</t>
+          <t>3048080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6148475</t>
+          <t>6150129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6233510</t>
+          <t>6231622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2012</t>
+          <t>Población con diagnóstico de varices en las piernas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33571</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169075</t>
+          <t>169501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221608</t>
+          <t>219347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187358</t>
+          <t>185857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245158</t>
+          <t>244716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>941072</t>
+          <t>941074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>961224</t>
+          <t>961517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1116189</t>
+          <t>1118450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1168722</t>
+          <t>1168296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2067282</t>
+          <t>2067724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2125082</t>
+          <t>2126583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>29279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>72137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115136</t>
+          <t>111081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88445</t>
+          <t>89325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>132796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1936110</t>
+          <t>1934678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1954273</t>
+          <t>1954114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1639456</t>
+          <t>1643511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1680583</t>
+          <t>1682455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3586734</t>
+          <t>3585753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3630104</t>
+          <t>3629224</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>27534</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470710</t>
+          <t>470774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435434</t>
+          <t>435175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449909</t>
+          <t>449899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>912786</t>
+          <t>912279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>930077</t>
+          <t>930162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29603</t>
+          <t>29361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59492</t>
+          <t>56855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>266226</t>
+          <t>267153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>333811</t>
+          <t>333414</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305911</t>
+          <t>307070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>377508</t>
+          <t>376084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3360290</t>
+          <t>3362927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3390179</t>
+          <t>3390421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3217209</t>
+          <t>3217606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3284794</t>
+          <t>3283867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6593293</t>
+          <t>6594717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6664890</t>
+          <t>6663731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2016</t>
+          <t>Población con diagnóstico de varices en las piernas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>27877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97290</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140998</t>
+          <t>139373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113209</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157965</t>
+          <t>164032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726986</t>
+          <t>726470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>742929</t>
+          <t>742897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>853662</t>
+          <t>855287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>897370</t>
+          <t>898170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1591042</t>
+          <t>1584975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1635798</t>
+          <t>1636622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39688</t>
+          <t>40607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67980</t>
+          <t>69452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106698</t>
+          <t>107956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91212</t>
+          <t>92296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136783</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2036697</t>
+          <t>2035778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2058099</t>
+          <t>2058055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1881602</t>
+          <t>1880344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1920320</t>
+          <t>1918848</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3927902</t>
+          <t>3928465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3973473</t>
+          <t>3972389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36623</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532420</t>
+          <t>532844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544955</t>
+          <t>544974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>522485</t>
+          <t>521919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540328</t>
+          <t>540472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1059404</t>
+          <t>1060482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1082637</t>
+          <t>1082706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67378</t>
+          <t>67706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189183</t>
+          <t>190180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249719</t>
+          <t>250618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236097</t>
+          <t>238547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304821</t>
+          <t>308066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3310240</t>
+          <t>3309912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3339553</t>
+          <t>3339421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3282381</t>
+          <t>3281482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3342917</t>
+          <t>3341920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6604897</t>
+          <t>6601652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6673621</t>
+          <t>6671171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2023</t>
+          <t>Población con diagnóstico de varices en las piernas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26630</t>
+          <t>27097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119579</t>
+          <t>118972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151641</t>
+          <t>151583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152411</t>
+          <t>153081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191119</t>
+          <t>191926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464180</t>
+          <t>466126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487312</t>
+          <t>486845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601527</t>
+          <t>601585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633589</t>
+          <t>634196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1075991</t>
+          <t>1075184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1114699</t>
+          <t>1114029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>49483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87777</t>
+          <t>87423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132057</t>
+          <t>136562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>214753</t>
+          <t>217593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>211168</t>
+          <t>205797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>296900</t>
+          <t>295755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2201831</t>
+          <t>2202185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2242302</t>
+          <t>2240125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2020999</t>
+          <t>2018159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2103695</t>
+          <t>2099190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4228461</t>
+          <t>4229606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4314193</t>
+          <t>4319564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52597</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69510</t>
+          <t>68903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623208</t>
+          <t>623649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637151</t>
+          <t>637627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>607706</t>
+          <t>607444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>627475</t>
+          <t>626616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1237417</t>
+          <t>1238024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1260558</t>
+          <t>1260888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93196</t>
+          <t>93886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144161</t>
+          <t>144378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>296697</t>
+          <t>295067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>403038</t>
+          <t>404946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>425279</t>
+          <t>423922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534649</t>
+          <t>528675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3306012</t>
+          <t>3305795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3356977</t>
+          <t>3356287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3246186</t>
+          <t>3244278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3352527</t>
+          <t>3354157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6564748</t>
+          <t>6570722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6674118</t>
+          <t>6675475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1419-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>40441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69120</t>
+          <t>68174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200399</t>
+          <t>202534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257967</t>
+          <t>256430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251978</t>
+          <t>252533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>313166</t>
+          <t>317174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>962603</t>
+          <t>963549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>991733</t>
+          <t>991282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1057146</t>
+          <t>1058683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1114714</t>
+          <t>1112579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2033669</t>
+          <t>2029661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2094857</t>
+          <t>2094302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47756</t>
+          <t>49851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85555</t>
+          <t>85897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125146</t>
+          <t>125584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119380</t>
+          <t>116722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163981</t>
+          <t>164020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1645657</t>
+          <t>1643562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1669784</t>
+          <t>1668926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1462527</t>
+          <t>1462089</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1502118</t>
+          <t>1501776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3117105</t>
+          <t>3117066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3161706</t>
+          <t>3164364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19950</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42589</t>
+          <t>41848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56361</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530423</t>
+          <t>531377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545318</t>
+          <t>545744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>433823</t>
+          <t>434564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456462</t>
+          <t>456011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971459</t>
+          <t>971759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>997711</t>
+          <t>997670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80228</t>
+          <t>79996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119234</t>
+          <t>120579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>331117</t>
+          <t>326983</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>402712</t>
+          <t>400540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>424119</t>
+          <t>419464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505612</t>
+          <t>503578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3157309</t>
+          <t>3155964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3196315</t>
+          <t>3196547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2976485</t>
+          <t>2978657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3048080</t>
+          <t>3052214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6150129</t>
+          <t>6152163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6231622</t>
+          <t>6236277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>33950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169501</t>
+          <t>167417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219347</t>
+          <t>220140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185857</t>
+          <t>185794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244716</t>
+          <t>243806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>941074</t>
+          <t>940693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>961517</t>
+          <t>960771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1118450</t>
+          <t>1117657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1168296</t>
+          <t>1170380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2067724</t>
+          <t>2068634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2126583</t>
+          <t>2126646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72137</t>
+          <t>73607</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111081</t>
+          <t>113940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132796</t>
+          <t>130678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1934678</t>
+          <t>1936165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1954114</t>
+          <t>1953739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1643511</t>
+          <t>1640652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1682455</t>
+          <t>1680985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3585753</t>
+          <t>3587871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3629224</t>
+          <t>3630713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>26207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470774</t>
+          <t>468924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435175</t>
+          <t>435592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449899</t>
+          <t>450163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>912279</t>
+          <t>913606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>930162</t>
+          <t>930143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56855</t>
+          <t>56704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>267153</t>
+          <t>265809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>333414</t>
+          <t>332386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>307070</t>
+          <t>303923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>376084</t>
+          <t>378861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3362927</t>
+          <t>3363078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3390421</t>
+          <t>3391424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3217606</t>
+          <t>3218634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3283867</t>
+          <t>3285211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6594717</t>
+          <t>6591940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6663731</t>
+          <t>6666878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>96157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139373</t>
+          <t>140124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112385</t>
+          <t>112767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164032</t>
+          <t>161644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726470</t>
+          <t>727172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>742897</t>
+          <t>743239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>855287</t>
+          <t>854536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>898170</t>
+          <t>898503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1584975</t>
+          <t>1587363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1636622</t>
+          <t>1636240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40607</t>
+          <t>40089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69452</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107956</t>
+          <t>106812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92296</t>
+          <t>92256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136220</t>
+          <t>137444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2035778</t>
+          <t>2036296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2058055</t>
+          <t>2058177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1880344</t>
+          <t>1881488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1918848</t>
+          <t>1919533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3928465</t>
+          <t>3927241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3972389</t>
+          <t>3972429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>25879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35545</t>
+          <t>35196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532844</t>
+          <t>530966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544974</t>
+          <t>544401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521919</t>
+          <t>523261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540472</t>
+          <t>540462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1060482</t>
+          <t>1060831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1082706</t>
+          <t>1082615</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>69299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190180</t>
+          <t>189385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250618</t>
+          <t>247390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>238547</t>
+          <t>236075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308066</t>
+          <t>308390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3309912</t>
+          <t>3308319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3339421</t>
+          <t>3338152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3281482</t>
+          <t>3284710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3341920</t>
+          <t>3342715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6601652</t>
+          <t>6601328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6671171</t>
+          <t>6673643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27097</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>135242</t>
+          <t>147933</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118972</t>
+          <t>131748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151583</t>
+          <t>165699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>171627</t>
+          <t>186502</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>166812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191926</t>
+          <t>208589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>477558</t>
+          <t>538973</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466126</t>
+          <t>526146</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486845</t>
+          <t>549140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>617926</t>
+          <t>673382</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601585</t>
+          <t>655616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>634196</t>
+          <t>689567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1095483</t>
+          <t>1212355</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1075184</t>
+          <t>1190268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1114029</t>
+          <t>1232045</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267110</t>
+          <t>1398857</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267110</t>
+          <t>1398857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267110</t>
+          <t>1398857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69931</t>
+          <t>77874</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49483</t>
+          <t>61115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87423</t>
+          <t>95265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>187435</t>
+          <t>206977</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136562</t>
+          <t>186210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217593</t>
+          <t>230682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>257365</t>
+          <t>284851</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205797</t>
+          <t>258489</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295755</t>
+          <t>314063</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2219677</t>
+          <t>2151824</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2202185</t>
+          <t>2134433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2240125</t>
+          <t>2168583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2048317</t>
+          <t>1962376</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2018159</t>
+          <t>1938671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2099190</t>
+          <t>1983143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4267996</t>
+          <t>4114200</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4229606</t>
+          <t>4084988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4319564</t>
+          <t>4140562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289608</t>
+          <t>2229698</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289608</t>
+          <t>2229698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289608</t>
+          <t>2229698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235752</t>
+          <t>2169353</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235752</t>
+          <t>2169353</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235752</t>
+          <t>2169353</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4525361</t>
+          <t>4399051</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4525361</t>
+          <t>4399051</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4525361</t>
+          <t>4399051</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42183</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52859</t>
+          <t>62099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57122</t>
+          <t>67664</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46039</t>
+          <t>55139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68903</t>
+          <t>83759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>631684</t>
+          <t>693439</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623649</t>
+          <t>683966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637627</t>
+          <t>699643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>618120</t>
+          <t>684679</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>607444</t>
+          <t>672096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626616</t>
+          <t>694413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1249805</t>
+          <t>1378118</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1238024</t>
+          <t>1362023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1260888</t>
+          <t>1390643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>121254</t>
+          <t>134591</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93886</t>
+          <t>114003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144378</t>
+          <t>158495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>364860</t>
+          <t>404425</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295067</t>
+          <t>375075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>404946</t>
+          <t>435142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>486114</t>
+          <t>539016</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>423922</t>
+          <t>504173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528675</t>
+          <t>575675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3328919</t>
+          <t>3384236</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3305795</t>
+          <t>3360332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3356287</t>
+          <t>3404824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3284364</t>
+          <t>3320438</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3244278</t>
+          <t>3289721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3354157</t>
+          <t>3349788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6613283</t>
+          <t>6704674</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6570722</t>
+          <t>6668015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6675475</t>
+          <t>6739517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450173</t>
+          <t>3518827</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450173</t>
+          <t>3518827</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450173</t>
+          <t>3518827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3724863</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3724863</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3724863</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099397</t>
+          <t>7243690</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099397</t>
+          <t>7243690</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099397</t>
+          <t>7243690</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
